--- a/血常规报告汇总.xlsx
+++ b/血常规报告汇总.xlsx
@@ -189,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$33</f>
+              <f>'趋势图'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$B$2:$B$33</f>
+              <f>'趋势图'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -300,12 +300,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$33</f>
+              <f>'趋势图'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$C$2:$C$33</f>
+              <f>'趋势图'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -411,12 +411,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$33</f>
+              <f>'趋势图'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$D$2:$D$33</f>
+              <f>'趋势图'!$D$2:$D$45</f>
             </numRef>
           </val>
         </ser>
@@ -522,12 +522,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$33</f>
+              <f>'趋势图'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$E$2:$E$33</f>
+              <f>'趋势图'!$E$2:$E$45</f>
             </numRef>
           </val>
         </ser>
@@ -633,12 +633,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'趋势图'!$A$2:$A$33</f>
+              <f>'趋势图'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'趋势图'!$F$2:$F$33</f>
+              <f>'趋势图'!$F$2:$F$45</f>
             </numRef>
           </val>
         </ser>
@@ -1108,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1855,6 +1855,270 @@
         <v>128</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1866,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2613,6 +2877,270 @@
         <v>128</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E34" t="n">
+        <v>44</v>
+      </c>
+      <c r="F34" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E35" t="n">
+        <v>59</v>
+      </c>
+      <c r="F35" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E36" t="n">
+        <v>65</v>
+      </c>
+      <c r="F36" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E37" t="n">
+        <v>73</v>
+      </c>
+      <c r="F37" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E38" t="n">
+        <v>105</v>
+      </c>
+      <c r="F38" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E39" t="n">
+        <v>105</v>
+      </c>
+      <c r="F39" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E40" t="n">
+        <v>127</v>
+      </c>
+      <c r="F40" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E41" t="n">
+        <v>108</v>
+      </c>
+      <c r="F41" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E42" t="n">
+        <v>106</v>
+      </c>
+      <c r="F42" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E43" t="n">
+        <v>88</v>
+      </c>
+      <c r="F43" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E44" t="n">
+        <v>84</v>
+      </c>
+      <c r="F44" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E45" t="n">
+        <v>79</v>
+      </c>
+      <c r="F45" t="n">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
